--- a/apoio/tabela_cores_final.xlsx
+++ b/apoio/tabela_cores_final.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://brasilbotoes.sharepoint.com/sites/Publico/Documentos Compartilhados/Estoque Pronta Entrega/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://brasilbotoes.sharepoint.com/sites/Publico/Documentos Compartilhados/Catálogo Pronta Entrega/Apoio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="11_5D3ECF77B45CF74A15CCC328BCB5BFC9E14674A5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62A7BF70-DFB8-4032-B27D-D82E61E9F24B}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="11_5D3ECF77B45CF74A15CCC328BCB5BFC9E14674A5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2962D33E-41B9-4A2B-9133-7D724A47E183}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cores" sheetId="1" r:id="rId1"/>
@@ -18,12 +18,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cores!$A$1:$F$148</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="559">
   <si>
     <t>cor_codigo</t>
   </si>
@@ -1682,6 +1695,24 @@
   </si>
   <si>
     <t>C001Pers5261</t>
+  </si>
+  <si>
+    <t>C2926</t>
+  </si>
+  <si>
+    <t>Leitoso Marrom</t>
+  </si>
+  <si>
+    <t>13660_C2926_4F.png</t>
+  </si>
+  <si>
+    <t>#F0EDE8</t>
+  </si>
+  <si>
+    <t>Botão bastão branco leitoso com veios naturais em marrom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1042 </t>
   </si>
 </sst>
 </file>
@@ -1701,6 +1732,7 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -2035,13 +2067,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F130"/>
+  <dimension ref="A1:F132"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="137.85546875" customWidth="1"/>
     <col min="6" max="6" width="26" bestFit="1" customWidth="1"/>
   </cols>
@@ -4641,6 +4673,37 @@
       </c>
       <c r="F130" t="s">
         <v>50</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>553</v>
+      </c>
+      <c r="B131" t="s">
+        <v>554</v>
+      </c>
+      <c r="C131" t="s">
+        <v>12</v>
+      </c>
+      <c r="D131" t="s">
+        <v>556</v>
+      </c>
+      <c r="E131" t="s">
+        <v>557</v>
+      </c>
+      <c r="F131" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>558</v>
+      </c>
+      <c r="B132" t="s">
+        <v>59</v>
+      </c>
+      <c r="C132" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/apoio/tabela_cores_final.xlsx
+++ b/apoio/tabela_cores_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://brasilbotoes.sharepoint.com/sites/Publico/Documentos Compartilhados/Catálogo Pronta Entrega/Apoio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="11_5D3ECF77B45CF74A15CCC328BCB5BFC9E14674A5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2962D33E-41B9-4A2B-9133-7D724A47E183}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="11_5D3ECF77B45CF74A15CCC328BCB5BFC9E14674A5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2C2E403-824E-4D4C-8961-A3B05999E497}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="558">
   <si>
     <t>cor_codigo</t>
   </si>
@@ -698,12 +698,6 @@
     <t>C1325</t>
   </si>
   <si>
-    <t>Azul petróleo</t>
-  </si>
-  <si>
-    <t>#0D3B3B</t>
-  </si>
-  <si>
     <t>Botão com textura rugosa e acabamento envelhecido, com pequenas inclusões brilhantes na superfície</t>
   </si>
   <si>
@@ -1713,6 +1707,9 @@
   </si>
   <si>
     <t xml:space="preserve">C1042 </t>
+  </si>
+  <si>
+    <t>Arroz</t>
   </si>
 </sst>
 </file>
@@ -2065,6 +2062,28 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="7">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{2DD851EB-F378-4DB5-B210-CD93A88B91F4}">
+  <we:reference id="WA200009404" version="1.0.0.8" store="Omex" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="WA200009404" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;94571d2e-8446-41f6-bc38-fba402008476&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F132"/>
@@ -2260,22 +2279,22 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B10" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C10" t="s">
         <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E10" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="F10" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2863,47 +2882,47 @@
         <v>219</v>
       </c>
       <c r="B40" t="s">
+        <v>557</v>
+      </c>
+      <c r="C40" t="s">
+        <v>44</v>
+      </c>
+      <c r="D40" t="s">
+        <v>164</v>
+      </c>
+      <c r="E40" t="s">
         <v>220</v>
       </c>
-      <c r="C40" t="s">
-        <v>24</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="F40" t="s">
         <v>221</v>
-      </c>
-      <c r="E40" t="s">
-        <v>222</v>
-      </c>
-      <c r="F40" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B41" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C41" t="s">
         <v>96</v>
       </c>
       <c r="D41" t="s">
+        <v>224</v>
+      </c>
+      <c r="E41" t="s">
+        <v>225</v>
+      </c>
+      <c r="F41" t="s">
         <v>226</v>
-      </c>
-      <c r="E41" t="s">
-        <v>227</v>
-      </c>
-      <c r="F41" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B42" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C42" t="s">
         <v>7</v>
@@ -2912,15 +2931,15 @@
         <v>8</v>
       </c>
       <c r="E42" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F42" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B43" t="s">
         <v>6</v>
@@ -2940,7 +2959,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B44" t="s">
         <v>11</v>
@@ -2960,30 +2979,30 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B45" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C45" t="s">
         <v>12</v>
       </c>
       <c r="D45" t="s">
+        <v>233</v>
+      </c>
+      <c r="E45" t="s">
+        <v>234</v>
+      </c>
+      <c r="F45" t="s">
         <v>235</v>
-      </c>
-      <c r="E45" t="s">
-        <v>236</v>
-      </c>
-      <c r="F45" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B46" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C46" t="s">
         <v>53</v>
@@ -2992,35 +3011,35 @@
         <v>54</v>
       </c>
       <c r="E46" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F46" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B47" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C47" t="s">
         <v>32</v>
       </c>
       <c r="D47" t="s">
+        <v>242</v>
+      </c>
+      <c r="E47" t="s">
+        <v>243</v>
+      </c>
+      <c r="F47" t="s">
         <v>244</v>
-      </c>
-      <c r="E47" t="s">
-        <v>245</v>
-      </c>
-      <c r="F47" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B48" t="s">
         <v>64</v>
@@ -3029,21 +3048,21 @@
         <v>12</v>
       </c>
       <c r="D48" t="s">
+        <v>246</v>
+      </c>
+      <c r="E48" t="s">
+        <v>247</v>
+      </c>
+      <c r="F48" t="s">
         <v>248</v>
-      </c>
-      <c r="E48" t="s">
-        <v>249</v>
-      </c>
-      <c r="F48" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B49" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C49" t="s">
         <v>184</v>
@@ -3052,35 +3071,35 @@
         <v>54</v>
       </c>
       <c r="E49" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F49" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B50" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C50" t="s">
         <v>96</v>
       </c>
       <c r="D50" t="s">
+        <v>255</v>
+      </c>
+      <c r="E50" t="s">
+        <v>256</v>
+      </c>
+      <c r="F50" t="s">
         <v>257</v>
-      </c>
-      <c r="E50" t="s">
-        <v>258</v>
-      </c>
-      <c r="F50" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B51" t="s">
         <v>52</v>
@@ -3092,18 +3111,18 @@
         <v>54</v>
       </c>
       <c r="E51" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F51" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B52" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C52" t="s">
         <v>12</v>
@@ -3112,18 +3131,18 @@
         <v>13</v>
       </c>
       <c r="E52" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F52" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B53" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C53" t="s">
         <v>53</v>
@@ -3132,75 +3151,75 @@
         <v>111</v>
       </c>
       <c r="E53" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F53" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>265</v>
+      </c>
+      <c r="B54" t="s">
+        <v>266</v>
+      </c>
+      <c r="C54" t="s">
         <v>267</v>
       </c>
-      <c r="B54" t="s">
+      <c r="D54" t="s">
         <v>268</v>
       </c>
-      <c r="C54" t="s">
+      <c r="E54" t="s">
         <v>269</v>
       </c>
-      <c r="D54" t="s">
+      <c r="F54" t="s">
         <v>270</v>
-      </c>
-      <c r="E54" t="s">
-        <v>271</v>
-      </c>
-      <c r="F54" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B55" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C55" t="s">
         <v>12</v>
       </c>
       <c r="D55" t="s">
+        <v>277</v>
+      </c>
+      <c r="E55" t="s">
+        <v>278</v>
+      </c>
+      <c r="F55" t="s">
         <v>279</v>
-      </c>
-      <c r="E55" t="s">
-        <v>280</v>
-      </c>
-      <c r="F55" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B56" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C56" t="s">
         <v>44</v>
       </c>
       <c r="D56" t="s">
+        <v>282</v>
+      </c>
+      <c r="E56" t="s">
+        <v>283</v>
+      </c>
+      <c r="F56" t="s">
         <v>284</v>
-      </c>
-      <c r="E56" t="s">
-        <v>285</v>
-      </c>
-      <c r="F56" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B57" t="s">
         <v>64</v>
@@ -3209,18 +3228,18 @@
         <v>12</v>
       </c>
       <c r="D57" t="s">
+        <v>286</v>
+      </c>
+      <c r="E57" t="s">
+        <v>287</v>
+      </c>
+      <c r="F57" t="s">
         <v>288</v>
-      </c>
-      <c r="E57" t="s">
-        <v>289</v>
-      </c>
-      <c r="F57" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B58" t="s">
         <v>64</v>
@@ -3229,18 +3248,18 @@
         <v>12</v>
       </c>
       <c r="D58" t="s">
+        <v>290</v>
+      </c>
+      <c r="E58" t="s">
+        <v>291</v>
+      </c>
+      <c r="F58" t="s">
         <v>292</v>
-      </c>
-      <c r="E58" t="s">
-        <v>293</v>
-      </c>
-      <c r="F58" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B59" t="s">
         <v>52</v>
@@ -3252,35 +3271,35 @@
         <v>54</v>
       </c>
       <c r="E59" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F59" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B60" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C60" t="s">
         <v>12</v>
       </c>
       <c r="D60" t="s">
+        <v>298</v>
+      </c>
+      <c r="E60" t="s">
+        <v>299</v>
+      </c>
+      <c r="F60" t="s">
         <v>300</v>
-      </c>
-      <c r="E60" t="s">
-        <v>301</v>
-      </c>
-      <c r="F60" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B61" t="s">
         <v>52</v>
@@ -3292,38 +3311,38 @@
         <v>54</v>
       </c>
       <c r="E61" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F61" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B62" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C62" t="s">
         <v>96</v>
       </c>
       <c r="D62" t="s">
+        <v>306</v>
+      </c>
+      <c r="E62" t="s">
+        <v>307</v>
+      </c>
+      <c r="F62" t="s">
         <v>308</v>
-      </c>
-      <c r="E62" t="s">
-        <v>309</v>
-      </c>
-      <c r="F62" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B63" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C63" t="s">
         <v>184</v>
@@ -3332,55 +3351,55 @@
         <v>185</v>
       </c>
       <c r="E63" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F63" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B64" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C64" t="s">
         <v>45</v>
       </c>
       <c r="D64" t="s">
+        <v>315</v>
+      </c>
+      <c r="E64" t="s">
+        <v>316</v>
+      </c>
+      <c r="F64" t="s">
         <v>317</v>
-      </c>
-      <c r="E64" t="s">
-        <v>318</v>
-      </c>
-      <c r="F64" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B65" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C65" t="s">
         <v>44</v>
       </c>
       <c r="D65" t="s">
+        <v>320</v>
+      </c>
+      <c r="E65" t="s">
+        <v>321</v>
+      </c>
+      <c r="F65" t="s">
         <v>322</v>
-      </c>
-      <c r="E65" t="s">
-        <v>323</v>
-      </c>
-      <c r="F65" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B66" t="s">
         <v>95</v>
@@ -3392,15 +3411,15 @@
         <v>133</v>
       </c>
       <c r="E66" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="F66" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B67" t="s">
         <v>64</v>
@@ -3412,55 +3431,55 @@
         <v>17</v>
       </c>
       <c r="E67" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F67" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B68" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C68" t="s">
         <v>44</v>
       </c>
       <c r="D68" t="s">
+        <v>331</v>
+      </c>
+      <c r="E68" t="s">
+        <v>332</v>
+      </c>
+      <c r="F68" t="s">
         <v>333</v>
-      </c>
-      <c r="E68" t="s">
-        <v>334</v>
-      </c>
-      <c r="F68" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B69" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C69" t="s">
         <v>44</v>
       </c>
       <c r="D69" t="s">
+        <v>336</v>
+      </c>
+      <c r="E69" t="s">
+        <v>337</v>
+      </c>
+      <c r="F69" t="s">
         <v>338</v>
-      </c>
-      <c r="E69" t="s">
-        <v>339</v>
-      </c>
-      <c r="F69" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B70" t="s">
         <v>95</v>
@@ -3469,41 +3488,41 @@
         <v>96</v>
       </c>
       <c r="D70" t="s">
+        <v>340</v>
+      </c>
+      <c r="E70" t="s">
+        <v>341</v>
+      </c>
+      <c r="F70" t="s">
         <v>342</v>
-      </c>
-      <c r="E70" t="s">
-        <v>343</v>
-      </c>
-      <c r="F70" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B71" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C71" t="s">
         <v>53</v>
       </c>
       <c r="D71" t="s">
+        <v>345</v>
+      </c>
+      <c r="E71" t="s">
+        <v>346</v>
+      </c>
+      <c r="F71" t="s">
         <v>347</v>
-      </c>
-      <c r="E71" t="s">
-        <v>348</v>
-      </c>
-      <c r="F71" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B72" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C72" t="s">
         <v>53</v>
@@ -3512,75 +3531,75 @@
         <v>54</v>
       </c>
       <c r="E72" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="F72" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B73" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C73" t="s">
         <v>53</v>
       </c>
       <c r="D73" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E73" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F73" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B74" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C74" t="s">
         <v>12</v>
       </c>
       <c r="D74" t="s">
+        <v>355</v>
+      </c>
+      <c r="E74" t="s">
+        <v>356</v>
+      </c>
+      <c r="F74" t="s">
         <v>357</v>
-      </c>
-      <c r="E74" t="s">
-        <v>358</v>
-      </c>
-      <c r="F74" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B75" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C75" t="s">
         <v>143</v>
       </c>
       <c r="D75" t="s">
+        <v>360</v>
+      </c>
+      <c r="E75" t="s">
+        <v>361</v>
+      </c>
+      <c r="F75" t="s">
         <v>362</v>
-      </c>
-      <c r="E75" t="s">
-        <v>363</v>
-      </c>
-      <c r="F75" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B76" t="s">
         <v>189</v>
@@ -3589,101 +3608,101 @@
         <v>190</v>
       </c>
       <c r="D76" t="s">
+        <v>364</v>
+      </c>
+      <c r="E76" t="s">
+        <v>365</v>
+      </c>
+      <c r="F76" t="s">
         <v>366</v>
-      </c>
-      <c r="E76" t="s">
-        <v>367</v>
-      </c>
-      <c r="F76" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B77" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C77" t="s">
         <v>24</v>
       </c>
       <c r="D77" t="s">
+        <v>369</v>
+      </c>
+      <c r="E77" t="s">
+        <v>370</v>
+      </c>
+      <c r="F77" t="s">
         <v>371</v>
-      </c>
-      <c r="E77" t="s">
-        <v>372</v>
-      </c>
-      <c r="F77" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>372</v>
+      </c>
+      <c r="B78" t="s">
+        <v>373</v>
+      </c>
+      <c r="C78" t="s">
+        <v>267</v>
+      </c>
+      <c r="D78" t="s">
         <v>374</v>
       </c>
-      <c r="B78" t="s">
+      <c r="E78" t="s">
         <v>375</v>
       </c>
-      <c r="C78" t="s">
-        <v>269</v>
-      </c>
-      <c r="D78" t="s">
+      <c r="F78" t="s">
         <v>376</v>
-      </c>
-      <c r="E78" t="s">
-        <v>377</v>
-      </c>
-      <c r="F78" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B79" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C79" t="s">
         <v>12</v>
       </c>
       <c r="D79" t="s">
+        <v>378</v>
+      </c>
+      <c r="E79" t="s">
+        <v>379</v>
+      </c>
+      <c r="F79" t="s">
         <v>380</v>
-      </c>
-      <c r="E79" t="s">
-        <v>381</v>
-      </c>
-      <c r="F79" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B80" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C80" t="s">
         <v>44</v>
       </c>
       <c r="D80" t="s">
+        <v>383</v>
+      </c>
+      <c r="E80" t="s">
+        <v>384</v>
+      </c>
+      <c r="F80" t="s">
         <v>385</v>
-      </c>
-      <c r="E80" t="s">
-        <v>386</v>
-      </c>
-      <c r="F80" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B81" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C81" t="s">
         <v>44</v>
@@ -3692,35 +3711,35 @@
         <v>172</v>
       </c>
       <c r="E81" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="F81" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B82" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C82" t="s">
         <v>59</v>
       </c>
       <c r="D82" t="s">
+        <v>392</v>
+      </c>
+      <c r="E82" t="s">
+        <v>393</v>
+      </c>
+      <c r="F82" t="s">
         <v>394</v>
-      </c>
-      <c r="E82" t="s">
-        <v>395</v>
-      </c>
-      <c r="F82" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B83" t="s">
         <v>163</v>
@@ -3729,38 +3748,38 @@
         <v>44</v>
       </c>
       <c r="D83" t="s">
+        <v>396</v>
+      </c>
+      <c r="E83" t="s">
+        <v>397</v>
+      </c>
+      <c r="F83" t="s">
         <v>398</v>
-      </c>
-      <c r="E83" t="s">
-        <v>399</v>
-      </c>
-      <c r="F83" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B84" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C84" t="s">
         <v>24</v>
       </c>
       <c r="D84" t="s">
+        <v>401</v>
+      </c>
+      <c r="E84" t="s">
+        <v>402</v>
+      </c>
+      <c r="F84" t="s">
         <v>403</v>
-      </c>
-      <c r="E84" t="s">
-        <v>404</v>
-      </c>
-      <c r="F84" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B85" t="s">
         <v>64</v>
@@ -3769,18 +3788,18 @@
         <v>12</v>
       </c>
       <c r="D85" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E85" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="F85" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B86" t="s">
         <v>76</v>
@@ -3789,38 +3808,38 @@
         <v>24</v>
       </c>
       <c r="D86" t="s">
+        <v>408</v>
+      </c>
+      <c r="E86" t="s">
+        <v>409</v>
+      </c>
+      <c r="F86" t="s">
         <v>410</v>
-      </c>
-      <c r="E86" t="s">
-        <v>411</v>
-      </c>
-      <c r="F86" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B87" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C87" t="s">
         <v>44</v>
       </c>
       <c r="D87" t="s">
+        <v>412</v>
+      </c>
+      <c r="E87" t="s">
+        <v>413</v>
+      </c>
+      <c r="F87" t="s">
         <v>414</v>
-      </c>
-      <c r="E87" t="s">
-        <v>415</v>
-      </c>
-      <c r="F87" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B88" t="s">
         <v>64</v>
@@ -3829,18 +3848,18 @@
         <v>12</v>
       </c>
       <c r="D88" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E88" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="F88" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B89" t="s">
         <v>58</v>
@@ -3855,15 +3874,15 @@
         <v>83</v>
       </c>
       <c r="F89" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B90" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C90" t="s">
         <v>44</v>
@@ -3872,18 +3891,18 @@
         <v>172</v>
       </c>
       <c r="E90" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="F90" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B91" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C91" t="s">
         <v>59</v>
@@ -3892,15 +3911,15 @@
         <v>125</v>
       </c>
       <c r="E91" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="F91" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B92" t="s">
         <v>23</v>
@@ -3920,7 +3939,7 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B93" t="s">
         <v>64</v>
@@ -3929,78 +3948,78 @@
         <v>12</v>
       </c>
       <c r="D93" t="s">
+        <v>428</v>
+      </c>
+      <c r="E93" t="s">
+        <v>429</v>
+      </c>
+      <c r="F93" t="s">
         <v>430</v>
-      </c>
-      <c r="E93" t="s">
-        <v>431</v>
-      </c>
-      <c r="F93" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>540</v>
+      </c>
+      <c r="B94" t="s">
+        <v>541</v>
+      </c>
+      <c r="C94" t="s">
+        <v>267</v>
+      </c>
+      <c r="D94" t="s">
+        <v>453</v>
+      </c>
+      <c r="E94" t="s">
         <v>542</v>
       </c>
-      <c r="B94" t="s">
+      <c r="F94" t="s">
         <v>543</v>
-      </c>
-      <c r="C94" t="s">
-        <v>269</v>
-      </c>
-      <c r="D94" t="s">
-        <v>455</v>
-      </c>
-      <c r="E94" t="s">
-        <v>544</v>
-      </c>
-      <c r="F94" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B95" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C95" t="s">
         <v>7</v>
       </c>
       <c r="D95" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E95" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="F95" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B96" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C96" t="s">
         <v>44</v>
       </c>
       <c r="D96" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E96" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F96" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B97" t="s">
         <v>52</v>
@@ -4012,78 +4031,78 @@
         <v>54</v>
       </c>
       <c r="E97" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="F97" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B98" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C98" t="s">
         <v>12</v>
       </c>
       <c r="D98" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E98" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="F98" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B99" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C99" t="s">
         <v>45</v>
       </c>
       <c r="D99" t="s">
+        <v>448</v>
+      </c>
+      <c r="E99" t="s">
+        <v>449</v>
+      </c>
+      <c r="F99" t="s">
         <v>450</v>
-      </c>
-      <c r="E99" t="s">
-        <v>451</v>
-      </c>
-      <c r="F99" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>451</v>
+      </c>
+      <c r="B100" t="s">
+        <v>452</v>
+      </c>
+      <c r="C100" t="s">
+        <v>267</v>
+      </c>
+      <c r="D100" t="s">
         <v>453</v>
       </c>
-      <c r="B100" t="s">
+      <c r="E100" t="s">
         <v>454</v>
       </c>
-      <c r="C100" t="s">
-        <v>269</v>
-      </c>
-      <c r="D100" t="s">
+      <c r="F100" t="s">
         <v>455</v>
-      </c>
-      <c r="E100" t="s">
-        <v>456</v>
-      </c>
-      <c r="F100" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B101" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C101" t="s">
         <v>53</v>
@@ -4092,95 +4111,95 @@
         <v>54</v>
       </c>
       <c r="E101" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F101" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B102" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C102" t="s">
         <v>143</v>
       </c>
       <c r="D102" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F102" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B103" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C103" t="s">
         <v>24</v>
       </c>
       <c r="D103" t="s">
+        <v>466</v>
+      </c>
+      <c r="E103" t="s">
+        <v>467</v>
+      </c>
+      <c r="F103" t="s">
         <v>468</v>
-      </c>
-      <c r="E103" t="s">
-        <v>469</v>
-      </c>
-      <c r="F103" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>469</v>
+      </c>
+      <c r="B104" t="s">
+        <v>452</v>
+      </c>
+      <c r="C104" t="s">
+        <v>267</v>
+      </c>
+      <c r="D104" t="s">
+        <v>453</v>
+      </c>
+      <c r="E104" t="s">
+        <v>470</v>
+      </c>
+      <c r="F104" t="s">
         <v>471</v>
-      </c>
-      <c r="B104" t="s">
-        <v>454</v>
-      </c>
-      <c r="C104" t="s">
-        <v>269</v>
-      </c>
-      <c r="D104" t="s">
-        <v>455</v>
-      </c>
-      <c r="E104" t="s">
-        <v>472</v>
-      </c>
-      <c r="F104" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B105" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C105" t="s">
         <v>24</v>
       </c>
       <c r="D105" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E105" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F105" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B106" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C106" t="s">
         <v>24</v>
@@ -4189,115 +4208,115 @@
         <v>37</v>
       </c>
       <c r="E106" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="F106" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B107" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C107" t="s">
         <v>32</v>
       </c>
       <c r="D107" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E107" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="F107" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B108" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C108" t="s">
         <v>190</v>
       </c>
       <c r="D108" t="s">
+        <v>485</v>
+      </c>
+      <c r="E108" t="s">
+        <v>486</v>
+      </c>
+      <c r="F108" t="s">
         <v>487</v>
-      </c>
-      <c r="E108" t="s">
-        <v>488</v>
-      </c>
-      <c r="F108" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B109" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C109" t="s">
         <v>143</v>
       </c>
       <c r="D109" t="s">
+        <v>490</v>
+      </c>
+      <c r="E109" t="s">
+        <v>491</v>
+      </c>
+      <c r="F109" t="s">
         <v>492</v>
-      </c>
-      <c r="E109" t="s">
-        <v>493</v>
-      </c>
-      <c r="F109" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>493</v>
+      </c>
+      <c r="B110" t="s">
+        <v>494</v>
+      </c>
+      <c r="C110" t="s">
+        <v>267</v>
+      </c>
+      <c r="D110" t="s">
         <v>495</v>
       </c>
-      <c r="B110" t="s">
+      <c r="E110" t="s">
         <v>496</v>
       </c>
-      <c r="C110" t="s">
-        <v>269</v>
-      </c>
-      <c r="D110" t="s">
+      <c r="F110" t="s">
         <v>497</v>
-      </c>
-      <c r="E110" t="s">
-        <v>498</v>
-      </c>
-      <c r="F110" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B111" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C111" t="s">
         <v>24</v>
       </c>
       <c r="D111" t="s">
+        <v>500</v>
+      </c>
+      <c r="E111" t="s">
+        <v>501</v>
+      </c>
+      <c r="F111" t="s">
         <v>502</v>
-      </c>
-      <c r="E111" t="s">
-        <v>503</v>
-      </c>
-      <c r="F111" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B112" t="s">
         <v>81</v>
@@ -4309,35 +4328,35 @@
         <v>77</v>
       </c>
       <c r="E112" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="F112" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B113" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C113" t="s">
         <v>32</v>
       </c>
       <c r="D113" t="s">
+        <v>508</v>
+      </c>
+      <c r="E113" t="s">
+        <v>509</v>
+      </c>
+      <c r="F113" t="s">
         <v>510</v>
-      </c>
-      <c r="E113" t="s">
-        <v>511</v>
-      </c>
-      <c r="F113" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B114" t="s">
         <v>16</v>
@@ -4357,10 +4376,10 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B115" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C115" t="s">
         <v>7</v>
@@ -4369,35 +4388,35 @@
         <v>8</v>
       </c>
       <c r="E115" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="F115" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B116" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C116" t="s">
         <v>12</v>
       </c>
       <c r="D116" t="s">
+        <v>516</v>
+      </c>
+      <c r="E116" t="s">
+        <v>517</v>
+      </c>
+      <c r="F116" t="s">
         <v>518</v>
-      </c>
-      <c r="E116" t="s">
-        <v>519</v>
-      </c>
-      <c r="F116" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B117" t="s">
         <v>28</v>
@@ -4417,7 +4436,7 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B118" t="s">
         <v>33</v>
@@ -4437,7 +4456,7 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B119" t="s">
         <v>28</v>
@@ -4457,7 +4476,7 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B120" t="s">
         <v>40</v>
@@ -4477,7 +4496,7 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B121" t="s">
         <v>64</v>
@@ -4486,38 +4505,38 @@
         <v>12</v>
       </c>
       <c r="D121" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E121" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F121" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B122" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C122" t="s">
         <v>96</v>
       </c>
       <c r="D122" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E122" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F122" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B123" t="s">
         <v>52</v>
@@ -4529,15 +4548,15 @@
         <v>54</v>
       </c>
       <c r="E123" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="F123" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B124" t="s">
         <v>200</v>
@@ -4549,18 +4568,18 @@
         <v>8</v>
       </c>
       <c r="E124" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="F124" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B125" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C125" t="s">
         <v>53</v>
@@ -4569,18 +4588,18 @@
         <v>54</v>
       </c>
       <c r="E125" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="F125" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B126" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C126" t="s">
         <v>53</v>
@@ -4589,15 +4608,15 @@
         <v>111</v>
       </c>
       <c r="E126" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="F126" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B127" t="s">
         <v>52</v>
@@ -4609,35 +4628,35 @@
         <v>111</v>
       </c>
       <c r="E127" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="F127" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B128" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C128" t="s">
         <v>190</v>
       </c>
       <c r="D128" t="s">
+        <v>537</v>
+      </c>
+      <c r="E128" t="s">
+        <v>538</v>
+      </c>
+      <c r="F128" t="s">
         <v>539</v>
-      </c>
-      <c r="E128" t="s">
-        <v>540</v>
-      </c>
-      <c r="F128" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B129" t="s">
         <v>20</v>
@@ -4677,27 +4696,27 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B131" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C131" t="s">
         <v>12</v>
       </c>
       <c r="D131" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="E131" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="F131" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B132" t="s">
         <v>59</v>
@@ -4716,26 +4735,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="93e3e88d-1e9c-4823-b8a9-8811fa4a6063">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="f969d47a-c144-462c-a51e-f47a3404b7ea" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C85081395C3AD84FAC594AE006A1EB3E" ma:contentTypeVersion="13" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="bae51f38d74cbc823602c8159bc86a60">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="93e3e88d-1e9c-4823-b8a9-8811fa4a6063" xmlns:ns3="f969d47a-c144-462c-a51e-f47a3404b7ea" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3e3b648d7afc429b5bb61d7f6b9481e" ns2:_="" ns3:_="">
     <xsd:import namespace="93e3e88d-1e9c-4823-b8a9-8811fa4a6063"/>
@@ -4942,26 +4941,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDC86EED-1239-427B-95BE-6AFD262BD259}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="93e3e88d-1e9c-4823-b8a9-8811fa4a6063"/>
-    <ds:schemaRef ds:uri="f969d47a-c144-462c-a51e-f47a3404b7ea"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="93e3e88d-1e9c-4823-b8a9-8811fa4a6063">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="f969d47a-c144-462c-a51e-f47a3404b7ea" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F00DE6E3-2012-49D3-91F4-23D61BF282F9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A002CF63-79D2-4D68-A7B9-3F84ADA01B0E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4980,6 +4980,25 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDC86EED-1239-427B-95BE-6AFD262BD259}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="93e3e88d-1e9c-4823-b8a9-8811fa4a6063"/>
+    <ds:schemaRef ds:uri="f969d47a-c144-462c-a51e-f47a3404b7ea"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F00DE6E3-2012-49D3-91F4-23D61BF282F9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{9502fd7b-bb83-4cda-885c-fde5d2f0d3cd}" enabled="0" method="" siteId="{9502fd7b-bb83-4cda-885c-fde5d2f0d3cd}" removed="1"/>
